--- a/dataset_t6_grouped/results2/G4/G4_T6321_W0022F0002T0006Z000C1N56_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T6321_W0022F0002T0006Z000C1N56_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>47.37774027257873</v>
+        <v>7.698882794294043</v>
       </c>
       <c r="D2" t="n">
-        <v>47.43893764658569</v>
+        <v>7.708827367570174</v>
       </c>
       <c r="E2" t="n">
-        <v>1.557807734986406</v>
+        <v>0.2531437569352909</v>
       </c>
       <c r="F2" t="n">
-        <v>1.793126457748474</v>
+        <v>0.2913830493841271</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>44.04109307029102</v>
+        <v>7.156677623922291</v>
       </c>
       <c r="D3" t="n">
-        <v>43.66823038508119</v>
+        <v>7.096087437575693</v>
       </c>
       <c r="E3" t="n">
-        <v>1.557807734986406</v>
+        <v>0.2531437569352909</v>
       </c>
       <c r="F3" t="n">
-        <v>1.793126457748474</v>
+        <v>0.2913830493841271</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>47.31270432869568</v>
+        <v>7.688314453413049</v>
       </c>
       <c r="D4" t="n">
-        <v>47.5042726844008</v>
+        <v>7.719444311215129</v>
       </c>
       <c r="E4" t="n">
-        <v>1.557807734986406</v>
+        <v>0.2531437569352909</v>
       </c>
       <c r="F4" t="n">
-        <v>1.793126457748474</v>
+        <v>0.2913830493841271</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
